--- a/uloha5/uloha5.xlsx
+++ b/uloha5/uloha5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80A5805-4910-4444-BBAD-D4D9C8418233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B862F62-4BBE-47C3-AAE3-2E76F87A914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8723A23-BA11-4575-BB1C-5F3360D4DC3F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>osciloskop</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>+-5</t>
+  </si>
+  <si>
+    <t>R (ohm)</t>
+  </si>
+  <si>
+    <t>+-0,1</t>
   </si>
 </sst>
 </file>
@@ -2933,7 +2939,7 @@
         <v>2.84</v>
       </c>
       <c r="F9">
-        <f t="shared" ref="F9:F27" si="4">0.0015*E9+2*0.001</f>
+        <f t="shared" ref="F9:F19" si="4">0.0015*E9+2*0.001</f>
         <v>6.2599999999999999E-3</v>
       </c>
       <c r="J9">
@@ -3733,8 +3739,8 @@
         <v>5.62</v>
       </c>
       <c r="F29">
-        <f t="shared" si="5"/>
-        <v>2.843E-2</v>
+        <f>0.0015*E29+2*0.001</f>
+        <v>1.043E-2</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -3756,8 +3762,8 @@
         <v>5.96</v>
       </c>
       <c r="F30">
-        <f t="shared" si="5"/>
-        <v>2.894E-2</v>
+        <f>0.0015*E30+2*0.001</f>
+        <v>1.094E-2</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -3779,16 +3785,16 @@
         <v>6.63</v>
       </c>
       <c r="F31">
-        <f t="shared" si="5"/>
+        <f>0.0015*E31+2*0.01</f>
         <v>2.9944999999999999E-2</v>
       </c>
     </row>
-    <row r="43" spans="11:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="10:15" x14ac:dyDescent="0.3">
       <c r="K43" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="11:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="10:15" x14ac:dyDescent="0.3">
       <c r="K44" t="s">
         <v>18</v>
       </c>
@@ -3796,7 +3802,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="11:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="10:15" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>23</v>
+      </c>
       <c r="K45" t="s">
         <v>19</v>
       </c>
@@ -3807,12 +3816,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="11:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="10:15" x14ac:dyDescent="0.3">
+      <c r="J46">
+        <v>100</v>
+      </c>
       <c r="K46">
         <v>80</v>
       </c>
       <c r="L46">
-        <f>K46/100</f>
+        <f>K46/J46</f>
         <v>0.8</v>
       </c>
       <c r="N46">
@@ -3822,9 +3834,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="11:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="10:15" x14ac:dyDescent="0.3">
+      <c r="J47" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="K47" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="L47">
+        <f>5/K46*L46</f>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
